--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/VIRGINIA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/VIRGINIA_2020.xlsx
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C63">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C97">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C136">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C147">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C371">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C387">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C388">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C402">
